--- a/downloads/Giocatori_Titolari_Rigoristi_2026_27.xlsx
+++ b/downloads/Giocatori_Titolari_Rigoristi_2026_27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matortor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E6792C-0B77-4964-A005-D490EF9DC530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86561ED5-1084-43C9-8590-557D69CF801B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1007,7 +1007,7 @@
     <t>Halhal</t>
   </si>
   <si>
-    <t>Rrahmani AI.</t>
+    <t>Rrahmani A</t>
   </si>
 </sst>
 </file>

--- a/downloads/Giocatori_Titolari_Rigoristi_2026_27.xlsx
+++ b/downloads/Giocatori_Titolari_Rigoristi_2026_27.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matortor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86561ED5-1084-43C9-8590-557D69CF801B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D0695F-BA12-4B56-8FFE-E8ED25CDE681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="318">
   <si>
     <t>Squadra</t>
   </si>
@@ -1005,9 +1005,6 @@
   </si>
   <si>
     <t>Halhal</t>
-  </si>
-  <si>
-    <t>Rrahmani A</t>
   </si>
 </sst>
 </file>
@@ -5837,7 +5834,7 @@
         <v>280</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>318</v>
+        <v>202</v>
       </c>
       <c r="C286" s="6" t="s">
         <v>27</v>
